--- a/artfynd/A 12427-2023 artfynd.xlsx
+++ b/artfynd/A 12427-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12427-2023 artfynd.xlsx
+++ b/artfynd/A 12427-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107205613</v>
+        <v>107205614</v>
       </c>
       <c r="B2" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527795.1574848009</v>
+        <v>527849</v>
       </c>
       <c r="R2" t="n">
-        <v>7264586.932103593</v>
+        <v>7264440</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2022-06-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,6 +760,11 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Frodog granskog med relativt klena träd, relativt rikligt med gamla granstubbar - tydligt delvis avverkat tidigare. Med fuktiga partier</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107205614</v>
+        <v>115984355</v>
       </c>
       <c r="B3" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trollhobben, Ly lm</t>
+          <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527848.939298279</v>
+        <v>528027</v>
       </c>
       <c r="R3" t="n">
-        <v>7264439.636570392</v>
+        <v>7265008</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,40 +864,34 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Frodog granskog med relativt klena träd, relativt rikligt med gamla granstubbar - tydligt delvis avverkat tidigare. Med fuktiga partier</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>4334</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Elvira Weibull</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107205611</v>
+        <v>115984378</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,37 +899,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trollhobben, Ly lm</t>
+          <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527795.1574848009</v>
+        <v>528578</v>
       </c>
       <c r="R4" t="n">
-        <v>7264586.932103593</v>
+        <v>7264917</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,35 +970,34 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Frodog granskog med relativt klena träd, relativt rikligt med gamla granstubbar - tydligt delvis avverkat tidigare. Med fuktiga partier</t>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>4282</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Elvira Weibull</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107205610</v>
+        <v>115984383</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,37 +1005,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Trollhobben, Ly lm</t>
+          <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527795.1574848009</v>
+        <v>528018</v>
       </c>
       <c r="R5" t="n">
-        <v>7264586.932103593</v>
+        <v>7264904</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,22 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,73 +1076,72 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Frodog granskog med relativt klena träd, relativt rikligt med gamla granstubbar - tydligt delvis avverkat tidigare. Med fuktiga partier</t>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>4350</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Elvira Weibull</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107313303</v>
+        <v>115984414</v>
       </c>
       <c r="B6" t="n">
-        <v>94149</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>293</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrådmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cephalozia macounii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Austin) Austin</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>#14905_72667/Cm98 (Trollhobben), Ly lm</t>
+          <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527795.1574848009</v>
+        <v>527782</v>
       </c>
       <c r="R6" t="n">
-        <v>7264586.932103593</v>
+        <v>7264856</v>
       </c>
       <c r="S6" t="n">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,34 +1163,14 @@
           <t>Tärna</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>14905_72667</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>EJ FUNNEN! Eftersökt inom en hel ha-ruta. Inga riktigt bra lågor i rutan. Lågor - Gran 25 (färre än förväntat pga äldre avverkning), Tall 0, löv 5 (björk). Stubbar -  Tall 0. Ingen levande tall.</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,39 +1182,34 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Frodog granskog med relativt klena träd, relativt rikligt med gamla granstubbar - tydligt delvis avverkat tidigare. Med fuktiga partier</t>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>4399</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Elvira Weibull</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115984393</v>
+        <v>115984420</v>
       </c>
       <c r="B7" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1319,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528012</v>
+        <v>527751</v>
       </c>
       <c r="R7" t="n">
-        <v>7264891</v>
+        <v>7264848</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1368,7 +1290,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1379,7 +1301,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1390,15 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115984331</v>
+        <v>115984422</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1430,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528262</v>
+        <v>527717</v>
       </c>
       <c r="R8" t="n">
-        <v>7265097</v>
+        <v>7264820</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1479,7 +1396,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1501,15 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115984428</v>
+        <v>115984441</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527843</v>
+        <v>527536</v>
       </c>
       <c r="R9" t="n">
-        <v>7264755</v>
+        <v>7264686</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1590,7 +1502,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1601,7 +1513,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1612,54 +1524,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115984361</v>
+        <v>115984494</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527919</v>
+        <v>527619</v>
       </c>
       <c r="R10" t="n">
-        <v>7264977</v>
+        <v>7264602</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1705,7 +1608,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1716,7 +1619,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1727,15 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115984339</v>
+        <v>115984324</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,39 +1641,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528054</v>
+        <v>528099</v>
       </c>
       <c r="R11" t="n">
-        <v>7265060</v>
+        <v>7265119</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1810,11 +1703,6 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackmärken på björk</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1826,7 +1714,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1848,37 +1736,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115984403</v>
+        <v>115984410</v>
       </c>
       <c r="B12" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527990</v>
+        <v>527756</v>
       </c>
       <c r="R12" t="n">
-        <v>7264882</v>
+        <v>7264859</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1937,7 +1820,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1948,7 +1831,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1959,37 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115984319</v>
+        <v>115984475</v>
       </c>
       <c r="B13" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>918</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528121</v>
+        <v>527633</v>
       </c>
       <c r="R13" t="n">
-        <v>7265123</v>
+        <v>7264615</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2048,7 +1926,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2059,7 +1937,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2070,15 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115984332</v>
+        <v>115984317</v>
       </c>
       <c r="B14" t="n">
-        <v>90355</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2110,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528300</v>
+        <v>528135</v>
       </c>
       <c r="R14" t="n">
-        <v>7265094</v>
+        <v>7265132</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2159,7 +2032,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2181,15 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115984382</v>
+        <v>115984338</v>
       </c>
       <c r="B15" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,21 +2065,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2221,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527757</v>
+        <v>528452</v>
       </c>
       <c r="R15" t="n">
-        <v>7264907</v>
+        <v>7265066</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2270,7 +2138,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2292,15 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115984425</v>
+        <v>115984362</v>
       </c>
       <c r="B16" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,21 +2171,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2195,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527671</v>
+        <v>528406</v>
       </c>
       <c r="R16" t="n">
-        <v>7264792</v>
+        <v>7264965</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2381,7 +2244,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2392,7 +2255,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2403,15 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115984384</v>
+        <v>115984403</v>
       </c>
       <c r="B17" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,21 +2277,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2443,10 +2301,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527757</v>
+        <v>527990</v>
       </c>
       <c r="R17" t="n">
-        <v>7264903</v>
+        <v>7264882</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2492,7 +2350,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2503,7 +2361,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2514,15 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115984420</v>
+        <v>115984434</v>
       </c>
       <c r="B18" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2554,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527751</v>
+        <v>527800</v>
       </c>
       <c r="R18" t="n">
-        <v>7264848</v>
+        <v>7264718</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2603,7 +2456,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2614,7 +2467,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2625,15 +2478,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115984422</v>
+        <v>115984538</v>
       </c>
       <c r="B19" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,21 +2489,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2665,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527717</v>
+        <v>527635</v>
       </c>
       <c r="R19" t="n">
-        <v>7264820</v>
+        <v>7264580</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2714,7 +2562,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2725,7 +2573,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2736,15 +2584,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115984324</v>
+        <v>115984354</v>
       </c>
       <c r="B20" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,21 +2595,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2776,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528099</v>
+        <v>528024</v>
       </c>
       <c r="R20" t="n">
-        <v>7265119</v>
+        <v>7265010</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2825,7 +2668,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2847,15 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115984424</v>
+        <v>115984411</v>
       </c>
       <c r="B21" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,21 +2701,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527878</v>
+        <v>527779</v>
       </c>
       <c r="R21" t="n">
-        <v>7264803</v>
+        <v>7264857</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2936,7 +2774,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2947,7 +2785,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2958,55 +2796,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115984356</v>
+        <v>115984332</v>
       </c>
       <c r="B22" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528007</v>
+        <v>528300</v>
       </c>
       <c r="R22" t="n">
-        <v>7265004</v>
+        <v>7265094</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3041,11 +2869,6 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hackmärken på gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3057,7 +2880,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3079,37 +2902,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115984426</v>
+        <v>115984375</v>
       </c>
       <c r="B23" t="n">
-        <v>104731</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3119,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527642</v>
+        <v>527858</v>
       </c>
       <c r="R23" t="n">
-        <v>7264774</v>
+        <v>7264928</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3168,7 +2986,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3190,37 +3008,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115984315</v>
+        <v>115984430</v>
       </c>
       <c r="B24" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3230,10 +3043,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528296</v>
+        <v>527797</v>
       </c>
       <c r="R24" t="n">
-        <v>7265142</v>
+        <v>7264728</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3279,7 +3092,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3290,7 +3103,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3301,19 +3114,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115984375</v>
+        <v>115984433</v>
       </c>
       <c r="B25" t="n">
-        <v>90355</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3341,10 +3149,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527858</v>
+        <v>527516</v>
       </c>
       <c r="R25" t="n">
-        <v>7264928</v>
+        <v>7264719</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3390,7 +3198,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3412,37 +3220,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115984325</v>
+        <v>115984439</v>
       </c>
       <c r="B26" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3452,10 +3255,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528298</v>
+        <v>527529</v>
       </c>
       <c r="R26" t="n">
-        <v>7265110</v>
+        <v>7264688</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3501,7 +3304,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3523,15 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115984369</v>
+        <v>115984319</v>
       </c>
       <c r="B27" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,21 +3337,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3563,10 +3361,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527768</v>
+        <v>528121</v>
       </c>
       <c r="R27" t="n">
-        <v>7264944</v>
+        <v>7265123</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3612,7 +3410,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3634,15 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115984423</v>
+        <v>115984386</v>
       </c>
       <c r="B28" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3674,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527693</v>
+        <v>527765</v>
       </c>
       <c r="R28" t="n">
-        <v>7264810</v>
+        <v>7264900</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3723,7 +3516,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3745,15 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115984414</v>
+        <v>115984387</v>
       </c>
       <c r="B29" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3761,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3785,10 +3573,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527782</v>
+        <v>527760</v>
       </c>
       <c r="R29" t="n">
-        <v>7264856</v>
+        <v>7264900</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3834,7 +3622,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3856,37 +3644,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115984432</v>
+        <v>115984399</v>
       </c>
       <c r="B30" t="n">
-        <v>104731</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221725</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527601</v>
+        <v>528010</v>
       </c>
       <c r="R30" t="n">
-        <v>7264720</v>
+        <v>7264885</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3945,7 +3728,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3956,7 +3739,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3967,15 +3750,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115984362</v>
+        <v>115984423</v>
       </c>
       <c r="B31" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3983,21 +3761,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4007,10 +3785,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528406</v>
+        <v>527693</v>
       </c>
       <c r="R31" t="n">
-        <v>7264965</v>
+        <v>7264810</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4056,7 +3834,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4067,7 +3845,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4078,15 +3856,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115984433</v>
+        <v>115984424</v>
       </c>
       <c r="B32" t="n">
-        <v>90355</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,21 +3867,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4118,10 +3891,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527516</v>
+        <v>527878</v>
       </c>
       <c r="R32" t="n">
-        <v>7264719</v>
+        <v>7264803</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4167,7 +3940,7 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4178,7 +3951,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4189,15 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115984326</v>
+        <v>115984474</v>
       </c>
       <c r="B33" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4205,21 +3973,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4229,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528269</v>
+        <v>527664</v>
       </c>
       <c r="R33" t="n">
-        <v>7265108</v>
+        <v>7264615</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4278,7 +4046,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4289,7 +4057,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4300,15 +4068,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115984345</v>
+        <v>115984336</v>
       </c>
       <c r="B34" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4316,21 +4079,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4103,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528430</v>
+        <v>528394</v>
       </c>
       <c r="R34" t="n">
-        <v>7265044</v>
+        <v>7265068</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4389,7 +4152,7 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4411,37 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115984321</v>
+        <v>115984388</v>
       </c>
       <c r="B35" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90692</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1599</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4451,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528111</v>
+        <v>528027</v>
       </c>
       <c r="R35" t="n">
-        <v>7265120</v>
+        <v>7264899</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4500,7 +4258,7 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4511,7 +4269,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4522,37 +4280,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115984342</v>
+        <v>115984507</v>
       </c>
       <c r="B36" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90692</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>1599</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4562,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528050</v>
+        <v>527625</v>
       </c>
       <c r="R36" t="n">
-        <v>7265053</v>
+        <v>7264595</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4611,7 +4364,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4622,7 +4375,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4633,15 +4386,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115984337</v>
+        <v>107205613</v>
       </c>
       <c r="B37" t="n">
-        <v>74459</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4649,37 +4397,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6428</v>
+        <v>2809</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gejmån - Ajaure, Ly lm</t>
+          <t>Trollhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528394</v>
+        <v>527795</v>
       </c>
       <c r="R37" t="n">
-        <v>7265068</v>
+        <v>7264587</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4703,12 +4451,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,39 +4468,30 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>4280</t>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Frodog granskog med relativt klena träd, relativt rikligt med gamla granstubbar - tydligt delvis avverkat tidigare. Med fuktiga partier</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Henrik Weibull, Elvira Weibull</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115984467</v>
+        <v>115984417</v>
       </c>
       <c r="B38" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4760,21 +4499,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4784,10 +4523,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527642</v>
+        <v>527756</v>
       </c>
       <c r="R38" t="n">
-        <v>7264624</v>
+        <v>7264853</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4833,7 +4572,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4844,7 +4583,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4855,37 +4594,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115984355</v>
+        <v>115984431</v>
       </c>
       <c r="B39" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4895,10 +4629,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528027</v>
+        <v>527611</v>
       </c>
       <c r="R39" t="n">
-        <v>7265008</v>
+        <v>7264720</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4944,7 +4678,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4966,37 +4700,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115984354</v>
+        <v>115984467</v>
       </c>
       <c r="B40" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5006,10 +4735,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528024</v>
+        <v>527642</v>
       </c>
       <c r="R40" t="n">
-        <v>7265010</v>
+        <v>7264624</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5055,7 +4784,7 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5066,7 +4795,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5077,53 +4806,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115984374</v>
+        <v>107205610</v>
       </c>
       <c r="B41" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gejmån - Ajaure, Ly lm</t>
+          <t>Trollhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527806</v>
+        <v>527795</v>
       </c>
       <c r="R41" t="n">
-        <v>7264931</v>
+        <v>7264587</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5147,12 +4871,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5164,79 +4888,65 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>4367</t>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Frodog granskog med relativt klena träd, relativt rikligt med gamla granstubbar - tydligt delvis avverkat tidigare. Med fuktiga partier</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Henrik Weibull, Elvira Weibull</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115984405</v>
+        <v>115984321</v>
       </c>
       <c r="B42" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527990</v>
+        <v>528111</v>
       </c>
       <c r="R42" t="n">
-        <v>7264880</v>
+        <v>7265120</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5282,7 +4992,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5293,7 +5003,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5304,55 +5014,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115984373</v>
+        <v>115984331</v>
       </c>
       <c r="B43" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527866</v>
+        <v>528262</v>
       </c>
       <c r="R43" t="n">
-        <v>7264933</v>
+        <v>7265097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5387,11 +5087,6 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hackmärken på gran</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5403,7 +5098,7 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5425,37 +5120,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115984434</v>
+        <v>115984369</v>
       </c>
       <c r="B44" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5465,10 +5155,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527800</v>
+        <v>527768</v>
       </c>
       <c r="R44" t="n">
-        <v>7264718</v>
+        <v>7264944</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5514,7 +5204,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5525,7 +5215,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5536,37 +5226,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>115984399</v>
+        <v>115984376</v>
       </c>
       <c r="B45" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5576,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528010</v>
+        <v>528076</v>
       </c>
       <c r="R45" t="n">
-        <v>7264885</v>
+        <v>7264923</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5625,7 +5310,7 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5647,37 +5332,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115984386</v>
+        <v>115984384</v>
       </c>
       <c r="B46" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5687,10 +5367,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527765</v>
+        <v>527757</v>
       </c>
       <c r="R46" t="n">
-        <v>7264900</v>
+        <v>7264903</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5736,7 +5416,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5758,37 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>115984455</v>
+        <v>115984428</v>
       </c>
       <c r="B47" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5798,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527719</v>
+        <v>527843</v>
       </c>
       <c r="R47" t="n">
-        <v>7264637</v>
+        <v>7264755</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5847,7 +5522,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5869,55 +5544,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>115984379</v>
+        <v>115984440</v>
       </c>
       <c r="B48" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527783</v>
+        <v>527517</v>
       </c>
       <c r="R48" t="n">
-        <v>7264914</v>
+        <v>7264688</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5952,11 +5617,6 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flera födosökande</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5968,7 +5628,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5990,37 +5650,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>115984376</v>
+        <v>115984337</v>
       </c>
       <c r="B49" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6030,10 +5685,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528076</v>
+        <v>528394</v>
       </c>
       <c r="R49" t="n">
-        <v>7264923</v>
+        <v>7265068</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6079,7 +5734,7 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6090,7 +5745,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6101,15 +5756,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>115984474</v>
+        <v>115984427</v>
       </c>
       <c r="B50" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6117,21 +5767,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6141,10 +5791,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527664</v>
+        <v>527815</v>
       </c>
       <c r="R50" t="n">
-        <v>7264615</v>
+        <v>7264761</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6190,7 +5840,7 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6212,37 +5862,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>115984388</v>
+        <v>115984374</v>
       </c>
       <c r="B51" t="n">
-        <v>89035</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1599</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6252,10 +5897,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528027</v>
+        <v>527806</v>
       </c>
       <c r="R51" t="n">
-        <v>7264899</v>
+        <v>7264931</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6301,7 +5946,7 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6312,7 +5957,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6323,15 +5968,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>115984431</v>
+        <v>115984455</v>
       </c>
       <c r="B52" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6339,21 +5979,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4769</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6363,10 +6003,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527611</v>
+        <v>527719</v>
       </c>
       <c r="R52" t="n">
-        <v>7264720</v>
+        <v>7264637</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6412,7 +6052,7 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6423,7 +6063,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6434,15 +6074,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>115984427</v>
+        <v>107205611</v>
       </c>
       <c r="B53" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6450,37 +6085,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gejmån - Ajaure, Ly lm</t>
+          <t>Trollhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527815</v>
+        <v>527795</v>
       </c>
       <c r="R53" t="n">
-        <v>7264761</v>
+        <v>7264587</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6504,12 +6139,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6521,39 +6156,30 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>4408</t>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Frodog granskog med relativt klena träd, relativt rikligt med gamla granstubbar - tydligt delvis avverkat tidigare. Med fuktiga partier</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Henrik Weibull, Elvira Weibull</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>115984360</v>
+        <v>115984314</v>
       </c>
       <c r="B54" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6561,34 +6187,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528312</v>
+        <v>528268</v>
       </c>
       <c r="R54" t="n">
-        <v>7264983</v>
+        <v>7265155</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6623,6 +6254,11 @@
           <t>2022-10-12</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Hackmärken på björk</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6634,7 +6270,7 @@
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6645,7 +6281,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6656,15 +6292,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>115984387</v>
+        <v>115984339</v>
       </c>
       <c r="B55" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6672,34 +6303,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527760</v>
+        <v>528054</v>
       </c>
       <c r="R55" t="n">
-        <v>7264900</v>
+        <v>7265060</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6734,6 +6370,11 @@
           <t>2022-10-12</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Hackmärken på björk</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6745,7 +6386,7 @@
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6767,15 +6408,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>115984336</v>
+        <v>115984356</v>
       </c>
       <c r="B56" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6783,34 +6419,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528394</v>
+        <v>528007</v>
       </c>
       <c r="R56" t="n">
-        <v>7265068</v>
+        <v>7265004</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6845,6 +6486,11 @@
           <t>2022-10-12</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Hackmärken på gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6856,7 +6502,7 @@
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6878,15 +6524,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>115984341</v>
+        <v>115984373</v>
       </c>
       <c r="B57" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6894,27 +6535,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6923,10 +6564,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527961</v>
+        <v>527866</v>
       </c>
       <c r="R57" t="n">
-        <v>7265057</v>
+        <v>7264933</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6963,7 +6604,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Flera ex födosökande, även svartmes.</t>
+          <t>Hackmärken på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6977,7 +6618,7 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6999,55 +6640,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>115984314</v>
+        <v>115984394</v>
       </c>
       <c r="B58" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528268</v>
+        <v>527823</v>
       </c>
       <c r="R58" t="n">
-        <v>7265155</v>
+        <v>7264890</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7084,7 +6715,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Hackmärken på björk</t>
+          <t>Tupp, satt i träd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7098,7 +6729,7 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7120,15 +6751,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>115984394</v>
+        <v>115984377</v>
       </c>
       <c r="B59" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7136,34 +6762,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527823</v>
+        <v>528580</v>
       </c>
       <c r="R59" t="n">
-        <v>7264890</v>
+        <v>7264918</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7198,11 +6829,6 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Tupp, satt i träd.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7214,7 +6840,7 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7225,7 +6851,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7236,50 +6862,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>115984411</v>
+        <v>115984416</v>
       </c>
       <c r="B60" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527779</v>
+        <v>527732</v>
       </c>
       <c r="R60" t="n">
-        <v>7264857</v>
+        <v>7264855</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7325,7 +6951,7 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7347,15 +6973,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>115984430</v>
+        <v>115984315</v>
       </c>
       <c r="B61" t="n">
-        <v>90355</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7363,21 +6984,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7387,10 +7008,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527797</v>
+        <v>528296</v>
       </c>
       <c r="R61" t="n">
-        <v>7264728</v>
+        <v>7265142</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7436,7 +7057,7 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7447,7 +7068,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7458,15 +7079,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>115984317</v>
+        <v>115984341</v>
       </c>
       <c r="B62" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7474,34 +7090,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528135</v>
+        <v>527961</v>
       </c>
       <c r="R62" t="n">
-        <v>7265132</v>
+        <v>7265057</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7536,6 +7157,11 @@
           <t>2022-10-12</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Flera ex födosökande, även svartmes.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7547,7 +7173,7 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7569,37 +7195,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>115984417</v>
+        <v>115984360</v>
       </c>
       <c r="B63" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7609,10 +7230,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527756</v>
+        <v>528312</v>
       </c>
       <c r="R63" t="n">
-        <v>7264853</v>
+        <v>7264983</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7658,7 +7279,7 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7669,7 +7290,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7680,15 +7301,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>115984383</v>
+        <v>115984379</v>
       </c>
       <c r="B64" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7696,34 +7312,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528018</v>
+        <v>527783</v>
       </c>
       <c r="R64" t="n">
-        <v>7264904</v>
+        <v>7264914</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7758,6 +7379,11 @@
           <t>2022-10-12</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Flera födosökande</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7769,7 +7395,7 @@
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7780,7 +7406,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7791,15 +7417,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>115984468</v>
+        <v>115984325</v>
       </c>
       <c r="B65" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7807,21 +7428,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7831,10 +7452,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527635</v>
+        <v>528298</v>
       </c>
       <c r="R65" t="n">
-        <v>7264622</v>
+        <v>7265110</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7880,7 +7501,7 @@
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7891,7 +7512,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7902,32 +7523,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>115984413</v>
+        <v>115984361</v>
       </c>
       <c r="B66" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7935,10 +7551,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7947,10 +7562,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527734</v>
+        <v>527919</v>
       </c>
       <c r="R66" t="n">
-        <v>7264857</v>
+        <v>7264977</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7996,7 +7611,7 @@
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8018,50 +7633,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>115984410</v>
+        <v>115984405</v>
       </c>
       <c r="B67" t="n">
-        <v>91117</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>918</v>
+        <v>103031</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527756</v>
+        <v>527990</v>
       </c>
       <c r="R67" t="n">
-        <v>7264859</v>
+        <v>7264880</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8107,7 +7722,7 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8118,7 +7733,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8129,15 +7744,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>115984416</v>
+        <v>115984413</v>
       </c>
       <c r="B68" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8145,21 +7755,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8174,10 +7784,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527732</v>
+        <v>527734</v>
       </c>
       <c r="R68" t="n">
-        <v>7264855</v>
+        <v>7264857</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8223,7 +7833,7 @@
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8238,6 +7848,218 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>115984426</v>
+      </c>
+      <c r="B69" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gejmån - Ajaure, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>527642</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7264774</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>4403</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>115984432</v>
+      </c>
+      <c r="B70" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gejmån - Ajaure, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>527601</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7264720</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>4405</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
